--- a/tiflow-chargeitem/build/0.9.0/StructureDefinition-GEM-ERPCHRG-PR-PAR-Patch-ChargeItem-Input.xlsx
+++ b/tiflow-chargeitem/build/0.9.0/StructureDefinition-GEM-ERPCHRG-PR-PAR-Patch-ChargeItem-Input.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2143" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2137" uniqueCount="257">
   <si>
     <t>Property</t>
   </si>
@@ -486,16 +486,6 @@
     <t>Meta.security</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>CE/CNE/CWE subset one of the sets of component 1-3 or 4-6</t>
-  </si>
-  <si>
-    <t>CV</t>
-  </si>
-  <si>
     <t>Parameters.meta.tag</t>
   </si>
   <si>
@@ -622,9 +612,6 @@
     <t>The name of the parameter (reference to the operation definition).</t>
   </si>
   <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
-  </si>
-  <si>
     <t>Parameters.parameter.value[x]</t>
   </si>
   <si>
@@ -638,8 +625,8 @@
     <t>If the parameter is a data type.</t>
   </si>
   <si>
-    <t>ele-1
-inv-1</t>
+    <t xml:space="preserve">inv-1
+</t>
   </si>
   <si>
     <t>Parameters.parameter.resource</t>
@@ -656,13 +643,6 @@
   </si>
   <si>
     <t>When resolving references in resources, the operation definition may specify how references may be resolved between parameters. If a reference cannot be resolved between the parameters, the application should fall back to it's general resource resolution methods.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inv-1
-</t>
-  </si>
-  <si>
-    <t>Entity. Role, or Act</t>
   </si>
   <si>
     <t>Parameters.parameter.part</t>
@@ -1189,7 +1169,7 @@
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="48.5546875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="24.1328125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="21.4140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -2483,24 +2463,24 @@
         <v>77</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>151</v>
+        <v>75</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>152</v>
+        <v>75</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>153</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2526,13 +2506,13 @@
         <v>143</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2558,31 +2538,31 @@
         <v>75</v>
       </c>
       <c r="X13" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="Z13" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF13" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="Y13" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>161</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
@@ -2591,24 +2571,24 @@
         <v>77</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>151</v>
+        <v>75</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>152</v>
+        <v>75</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>153</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2634,13 +2614,13 @@
         <v>125</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -2690,7 +2670,7 @@
         <v>75</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -2713,10 +2693,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2739,16 +2719,16 @@
         <v>75</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N15" t="s" s="2">
         <v>168</v>
-      </c>
-      <c r="L15" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2774,31 +2754,31 @@
         <v>75</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="Z15" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AA15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="Y15" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="Z15" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>175</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>76</v>
@@ -2821,10 +2801,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2847,13 +2827,13 @@
         <v>85</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2892,7 +2872,7 @@
         <v>75</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="AC16" s="2"/>
       <c r="AD16" t="s" s="2">
@@ -2902,7 +2882,7 @@
         <v>137</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
@@ -2911,24 +2891,24 @@
         <v>77</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>151</v>
+        <v>75</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3031,10 +3011,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3104,16 +3084,16 @@
         <v>75</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AF18" t="s" s="2">
         <v>111</v>
@@ -3139,14 +3119,14 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3168,16 +3148,16 @@
         <v>104</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>107</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>75</v>
@@ -3226,7 +3206,7 @@
         <v>75</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>76</v>
@@ -3244,15 +3224,15 @@
         <v>75</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3278,14 +3258,12 @@
         <v>98</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>194</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>75</v>
@@ -3334,7 +3312,7 @@
         <v>75</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>84</v>
@@ -3357,10 +3335,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3383,13 +3361,13 @@
         <v>85</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3440,16 +3418,16 @@
         <v>75</v>
       </c>
       <c r="AF21" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI21" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="AG21" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH21" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI21" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>96</v>
@@ -3458,15 +3436,15 @@
         <v>75</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3489,16 +3467,16 @@
         <v>85</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3548,7 +3526,7 @@
         <v>75</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
@@ -3557,7 +3535,7 @@
         <v>84</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>75</v>
@@ -3566,15 +3544,15 @@
         <v>75</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>206</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3600,13 +3578,13 @@
         <v>75</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -3656,7 +3634,7 @@
         <v>75</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -3668,7 +3646,7 @@
         <v>75</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>75</v>
@@ -3679,13 +3657,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>75</v>
@@ -3707,13 +3685,13 @@
         <v>85</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3764,7 +3742,7 @@
         <v>75</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
@@ -3773,24 +3751,24 @@
         <v>77</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>151</v>
+        <v>75</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3893,10 +3871,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3966,16 +3944,16 @@
         <v>75</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AF26" t="s" s="2">
         <v>111</v>
@@ -4001,14 +3979,14 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4030,16 +4008,16 @@
         <v>104</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="N27" t="s" s="2">
         <v>107</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>75</v>
@@ -4088,7 +4066,7 @@
         <v>75</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
@@ -4106,15 +4084,15 @@
         <v>75</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4140,14 +4118,12 @@
         <v>98</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>194</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>75</v>
@@ -4157,7 +4133,7 @@
         <v>75</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>75</v>
@@ -4196,7 +4172,7 @@
         <v>75</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>84</v>
@@ -4219,10 +4195,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4245,13 +4221,13 @@
         <v>85</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4302,16 +4278,16 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI29" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="AG29" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH29" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI29" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>96</v>
@@ -4320,15 +4296,15 @@
         <v>75</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4351,16 +4327,16 @@
         <v>85</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4410,7 +4386,7 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -4419,7 +4395,7 @@
         <v>84</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>75</v>
@@ -4428,15 +4404,15 @@
         <v>75</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>206</v>
+        <v>75</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4462,13 +4438,13 @@
         <v>75</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -4506,7 +4482,7 @@
         <v>75</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="AC31" s="2"/>
       <c r="AD31" t="s" s="2">
@@ -4516,7 +4492,7 @@
         <v>137</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -4528,7 +4504,7 @@
         <v>75</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>75</v>
@@ -4539,10 +4515,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4645,10 +4621,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4718,16 +4694,16 @@
         <v>75</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
         <v>111</v>
@@ -4753,14 +4729,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -4782,16 +4758,16 @@
         <v>104</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>107</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>75</v>
@@ -4840,7 +4816,7 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
@@ -4858,15 +4834,15 @@
         <v>75</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4892,14 +4868,12 @@
         <v>98</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>194</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>75</v>
@@ -4948,7 +4922,7 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>84</v>
@@ -4971,10 +4945,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4997,13 +4971,13 @@
         <v>85</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5054,16 +5028,16 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI36" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="AG36" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH36" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI36" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>96</v>
@@ -5072,15 +5046,15 @@
         <v>75</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5103,16 +5077,16 @@
         <v>85</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5162,7 +5136,7 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -5171,7 +5145,7 @@
         <v>84</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>75</v>
@@ -5180,15 +5154,15 @@
         <v>75</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>206</v>
+        <v>75</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5214,13 +5188,13 @@
         <v>75</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5270,7 +5244,7 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
@@ -5282,7 +5256,7 @@
         <v>75</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>75</v>
@@ -5293,13 +5267,13 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>75</v>
@@ -5321,16 +5295,16 @@
         <v>85</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5380,7 +5354,7 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -5392,7 +5366,7 @@
         <v>75</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>75</v>
@@ -5403,10 +5377,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5509,10 +5483,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5582,16 +5556,16 @@
         <v>75</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
         <v>111</v>
@@ -5617,14 +5591,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -5646,16 +5620,16 @@
         <v>104</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>107</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>75</v>
@@ -5704,7 +5678,7 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
@@ -5722,15 +5696,15 @@
         <v>75</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5756,14 +5730,12 @@
         <v>98</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>194</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>75</v>
@@ -5773,7 +5745,7 @@
         <v>75</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>75</v>
@@ -5812,7 +5784,7 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>84</v>
@@ -5835,10 +5807,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5861,13 +5833,13 @@
         <v>85</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5918,16 +5890,16 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI44" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="AG44" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI44" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>96</v>
@@ -5936,15 +5908,15 @@
         <v>75</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5967,16 +5939,16 @@
         <v>85</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6026,7 +5998,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -6035,7 +6007,7 @@
         <v>84</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>75</v>
@@ -6044,15 +6016,15 @@
         <v>75</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>206</v>
+        <v>75</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6078,13 +6050,13 @@
         <v>75</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6134,7 +6106,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -6146,7 +6118,7 @@
         <v>75</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>75</v>
@@ -6157,13 +6129,13 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>75</v>
@@ -6185,16 +6157,16 @@
         <v>85</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6244,7 +6216,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -6256,7 +6228,7 @@
         <v>75</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>75</v>
@@ -6267,10 +6239,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6373,10 +6345,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6446,16 +6418,16 @@
         <v>75</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
         <v>111</v>
@@ -6481,14 +6453,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -6510,16 +6482,16 @@
         <v>104</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="N50" t="s" s="2">
         <v>107</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>75</v>
@@ -6568,7 +6540,7 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -6586,15 +6558,15 @@
         <v>75</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6620,14 +6592,12 @@
         <v>98</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>194</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>75</v>
@@ -6637,7 +6607,7 @@
         <v>75</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>75</v>
@@ -6676,7 +6646,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>84</v>
@@ -6699,10 +6669,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6725,13 +6695,13 @@
         <v>85</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6782,16 +6752,16 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI52" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="AG52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI52" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>96</v>
@@ -6800,15 +6770,15 @@
         <v>75</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6831,16 +6801,16 @@
         <v>85</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -6890,7 +6860,7 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -6899,7 +6869,7 @@
         <v>84</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>75</v>
@@ -6908,15 +6878,15 @@
         <v>75</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>206</v>
+        <v>75</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6942,13 +6912,13 @@
         <v>75</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -6998,7 +6968,7 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -7010,7 +6980,7 @@
         <v>75</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>75</v>
@@ -7021,13 +6991,13 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="D55" t="s" s="2">
         <v>75</v>
@@ -7049,16 +7019,16 @@
         <v>85</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7108,7 +7078,7 @@
         <v>75</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
@@ -7120,7 +7090,7 @@
         <v>75</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>75</v>
@@ -7131,10 +7101,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7237,10 +7207,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7310,16 +7280,16 @@
         <v>75</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AF57" t="s" s="2">
         <v>111</v>
@@ -7345,14 +7315,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -7374,16 +7344,16 @@
         <v>104</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>107</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>75</v>
@@ -7432,7 +7402,7 @@
         <v>75</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>76</v>
@@ -7450,15 +7420,15 @@
         <v>75</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7484,14 +7454,12 @@
         <v>98</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>194</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>75</v>
@@ -7501,7 +7469,7 @@
         <v>75</v>
       </c>
       <c r="S59" t="s" s="2">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="T59" t="s" s="2">
         <v>75</v>
@@ -7540,7 +7508,7 @@
         <v>75</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>84</v>
@@ -7563,10 +7531,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7589,13 +7557,13 @@
         <v>85</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -7646,16 +7614,16 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI60" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="AG60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI60" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>96</v>
@@ -7664,15 +7632,15 @@
         <v>75</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7695,16 +7663,16 @@
         <v>85</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -7754,7 +7722,7 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>76</v>
@@ -7763,7 +7731,7 @@
         <v>84</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>75</v>
@@ -7772,15 +7740,15 @@
         <v>75</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>206</v>
+        <v>75</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7806,13 +7774,13 @@
         <v>75</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -7862,7 +7830,7 @@
         <v>75</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>76</v>
@@ -7874,7 +7842,7 @@
         <v>75</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>75</v>
